--- a/data/dividends_info_20260406.xlsx
+++ b/data/dividends_info_20260406.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K156"/>
+  <dimension ref="A1:K166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6319,11 +6319,11 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.43</v>
+        <v>0.16</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -6347,14 +6347,14 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>IT0003203947</t>
+          <t>IT0004093263</t>
         </is>
       </c>
       <c r="H126" t="n">
-        <v>10.39999961853027</v>
+        <v>3.470000028610229</v>
       </c>
       <c r="I126" t="n">
-        <v>4.134615536272179</v>
+        <v>4.610950970628137</v>
       </c>
       <c r="J126" t="n">
         <v>28</v>
@@ -6366,11 +6366,11 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.15</v>
+        <v>0.61</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -6394,14 +6394,14 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>IT0005322612</t>
+          <t>IT0004720733</t>
         </is>
       </c>
       <c r="H127" t="n">
-        <v>4.099999904632568</v>
+        <v>21.95000076293945</v>
       </c>
       <c r="I127" t="n">
-        <v>3.658536670464694</v>
+        <v>2.779043183588078</v>
       </c>
       <c r="J127" t="n">
         <v>28</v>
@@ -6413,11 +6413,11 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.197169</v>
+        <v>0.15</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -6441,14 +6441,14 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>IT0005455875</t>
+          <t>IT0005386369</t>
         </is>
       </c>
       <c r="H128" t="n">
-        <v>12.30000019073486</v>
+        <v>2.960000038146973</v>
       </c>
       <c r="I128" t="n">
-        <v>1.60299997514244</v>
+        <v>5.067567502259338</v>
       </c>
       <c r="J128" t="n">
         <v>28</v>
@@ -6460,11 +6460,11 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -6488,14 +6488,14 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>IT0005253205</t>
+          <t>IT0001268561</t>
         </is>
       </c>
       <c r="H129" t="n">
-        <v>26.79999923706055</v>
+        <v>11.85000038146973</v>
       </c>
       <c r="I129" t="n">
-        <v>4.10447772878612</v>
+        <v>5.907172805619612</v>
       </c>
       <c r="J129" t="n">
         <v>28</v>
@@ -6507,11 +6507,11 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5</v>
+        <v>0.5105</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -6535,14 +6535,14 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>IT0005075764</t>
+          <t>IT0001041000</t>
         </is>
       </c>
       <c r="H130" t="n">
-        <v>18.79999923706055</v>
+        <v>8.829999923706055</v>
       </c>
       <c r="I130" t="n">
-        <v>2.659574576015658</v>
+        <v>5.78142700352071</v>
       </c>
       <c r="J130" t="n">
         <v>28</v>
@@ -6554,15 +6554,15 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.47</v>
+        <v>0.27</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>EURO</t>
+          <t>DOLLARI USA</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6582,14 +6582,14 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>IT0005107492</t>
+          <t>LU2592315662</t>
         </is>
       </c>
       <c r="H131" t="n">
-        <v>40.54999923706055</v>
+        <v>7.949999809265137</v>
       </c>
       <c r="I131" t="n">
-        <v>1.159062907134274</v>
+        <v>3.396226496575949</v>
       </c>
       <c r="J131" t="n">
         <v>28</v>
@@ -6601,11 +6601,11 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.11</v>
+        <v>0.35</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -6629,14 +6629,14 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>IT0005339160</t>
+          <t>IT0003850929</t>
         </is>
       </c>
       <c r="H132" t="n">
-        <v>2.450000047683716</v>
+        <v>5.090000152587891</v>
       </c>
       <c r="I132" t="n">
-        <v>4.489795830983613</v>
+        <v>6.876227691703521</v>
       </c>
       <c r="J132" t="n">
         <v>28</v>
@@ -6648,11 +6648,11 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -6676,14 +6676,14 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>IT0005274094</t>
+          <t>IT0005203424</t>
         </is>
       </c>
       <c r="H133" t="n">
-        <v>78.59999847412109</v>
+        <v>37.20000076293945</v>
       </c>
       <c r="I133" t="n">
-        <v>1.526717586890409</v>
+        <v>2.956989186666567</v>
       </c>
       <c r="J133" t="n">
         <v>28</v>
@@ -6695,11 +6695,11 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.27</v>
+        <v>0.75</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -6718,19 +6718,19 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Straordinario</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>IT0005513202</t>
+          <t>IT0005252736</t>
         </is>
       </c>
       <c r="H134" t="n">
-        <v>23.29999923706055</v>
+        <v>18.70000076293945</v>
       </c>
       <c r="I134" t="n">
-        <v>1.158798321205706</v>
+        <v>4.010695023533825</v>
       </c>
       <c r="J134" t="n">
         <v>28</v>
@@ -6742,11 +6742,11 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -6770,14 +6770,14 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>IT0001018362</t>
+          <t>IT0003203947</t>
         </is>
       </c>
       <c r="H135" t="n">
-        <v>10.25</v>
+        <v>10.39999961853027</v>
       </c>
       <c r="I135" t="n">
-        <v>3.707317073170731</v>
+        <v>4.134615536272179</v>
       </c>
       <c r="J135" t="n">
         <v>28</v>
@@ -6789,11 +6789,11 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -6817,14 +6817,14 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>IT0005440893</t>
+          <t>IT0005322612</t>
         </is>
       </c>
       <c r="H136" t="n">
-        <v>26.79999923706055</v>
+        <v>4.099999904632568</v>
       </c>
       <c r="I136" t="n">
-        <v>1.119403016941669</v>
+        <v>3.658536670464694</v>
       </c>
       <c r="J136" t="n">
         <v>28</v>
@@ -6836,11 +6836,11 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.007</v>
+        <v>0.197169</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -6849,12 +6849,12 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -6864,30 +6864,30 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>IT0001073045</t>
+          <t>IT0005455875</t>
         </is>
       </c>
       <c r="H137" t="n">
-        <v>0.1529999971389771</v>
+        <v>12.30000019073486</v>
       </c>
       <c r="I137" t="n">
-        <v>4.575163484246064</v>
+        <v>1.60299997514244</v>
       </c>
       <c r="J137" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="K137" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.16</v>
+        <v>1.1</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -6896,12 +6896,12 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -6911,30 +6911,30 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>IT0001033700</t>
+          <t>IT0005253205</t>
         </is>
       </c>
       <c r="H138" t="n">
-        <v>6.650000095367432</v>
+        <v>26.79999923706055</v>
       </c>
       <c r="I138" t="n">
-        <v>2.406015003089403</v>
+        <v>4.10447772878612</v>
       </c>
       <c r="J138" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="K138" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.065</v>
+        <v>0.5</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -6943,12 +6943,12 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -6958,30 +6958,30 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>IT0003372205</t>
+          <t>IT0005075764</t>
         </is>
       </c>
       <c r="H139" t="n">
-        <v>2.214999914169312</v>
+        <v>18.79999923706055</v>
       </c>
       <c r="I139" t="n">
-        <v>2.93453735976224</v>
+        <v>2.659574576015658</v>
       </c>
       <c r="J139" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="K139" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.25</v>
+        <v>0.47</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -7005,30 +7005,30 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>IT0003365613</t>
+          <t>IT0005107492</t>
         </is>
       </c>
       <c r="H140" t="n">
-        <v>7.46999979019165</v>
+        <v>40.54999923706055</v>
       </c>
       <c r="I140" t="n">
-        <v>3.346720308188737</v>
+        <v>1.159062907134274</v>
       </c>
       <c r="J140" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="K140" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5</v>
+        <v>0.11</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -7037,12 +7037,12 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -7052,30 +7052,30 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>IT0004998065</t>
+          <t>IT0005339160</t>
         </is>
       </c>
       <c r="H141" t="n">
-        <v>6.639999866485596</v>
+        <v>2.450000047683716</v>
       </c>
       <c r="I141" t="n">
-        <v>7.530120633340297</v>
+        <v>4.489795830983613</v>
       </c>
       <c r="J141" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="K141" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.65</v>
+        <v>1.2</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -7084,12 +7084,12 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -7099,30 +7099,30 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>IT0004776628</t>
+          <t>IT0005274094</t>
         </is>
       </c>
       <c r="H142" t="n">
-        <v>17.72999954223633</v>
+        <v>78.59999847412109</v>
       </c>
       <c r="I142" t="n">
-        <v>3.666102745527843</v>
+        <v>1.526717586890409</v>
       </c>
       <c r="J142" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="K142" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.54</v>
+        <v>0.27</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -7131,12 +7131,12 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -7146,30 +7146,30 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>IT0005218380</t>
+          <t>IT0005513202</t>
         </is>
       </c>
       <c r="H143" t="n">
-        <v>12.05000019073486</v>
+        <v>23.29999923706055</v>
       </c>
       <c r="I143" t="n">
-        <v>4.481327729896645</v>
+        <v>1.158798321205706</v>
       </c>
       <c r="J143" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="K143" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.1</v>
+        <v>0.38</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -7193,30 +7193,30 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>NL0015435975</t>
+          <t>IT0001018362</t>
         </is>
       </c>
       <c r="H144" t="n">
-        <v>6.245999813079834</v>
+        <v>10.25</v>
       </c>
       <c r="I144" t="n">
-        <v>1.601024703692572</v>
+        <v>3.707317073170731</v>
       </c>
       <c r="J144" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="K144" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.16</v>
+        <v>0.3</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -7225,12 +7225,12 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -7240,30 +7240,30 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>IT0005215329</t>
+          <t>IT0005440893</t>
         </is>
       </c>
       <c r="H145" t="n">
-        <v>8.319999694824219</v>
+        <v>26.79999923706055</v>
       </c>
       <c r="I145" t="n">
-        <v>1.923076993614967</v>
+        <v>1.119403016941669</v>
       </c>
       <c r="J145" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="K145" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>3.615</v>
+        <v>0.007</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -7272,12 +7272,12 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -7287,30 +7287,30 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>NL0011585146</t>
+          <t>IT0001073045</t>
         </is>
       </c>
       <c r="H146" t="n">
-        <v>295.5</v>
+        <v>0.1529999971389771</v>
       </c>
       <c r="I146" t="n">
-        <v>1.223350253807107</v>
+        <v>4.575163484246064</v>
       </c>
       <c r="J146" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="K146" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>1.36</v>
+        <v>0.16</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -7319,12 +7319,12 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -7334,30 +7334,30 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>IT0005144784</t>
+          <t>IT0001033700</t>
         </is>
       </c>
       <c r="H147" t="n">
-        <v>27</v>
+        <v>6.650000095367432</v>
       </c>
       <c r="I147" t="n">
-        <v>5.037037037037037</v>
+        <v>2.406015003089403</v>
       </c>
       <c r="J147" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="K147" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.585</v>
+        <v>0.065</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -7366,12 +7366,12 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -7381,30 +7381,30 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>IT0004931058</t>
+          <t>IT0003372205</t>
         </is>
       </c>
       <c r="H148" t="n">
-        <v>13.84000015258789</v>
+        <v>2.214999914169312</v>
       </c>
       <c r="I148" t="n">
-        <v>4.226878566114849</v>
+        <v>2.93453735976224</v>
       </c>
       <c r="J148" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="K148" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.63</v>
+        <v>0.25</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -7413,12 +7413,12 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -7428,30 +7428,30 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>IT0000062957</t>
+          <t>IT0003365613</t>
         </is>
       </c>
       <c r="H149" t="n">
-        <v>16.53499984741211</v>
+        <v>7.46999979019165</v>
       </c>
       <c r="I149" t="n">
-        <v>3.810099823488061</v>
+        <v>3.346720308188737</v>
       </c>
       <c r="J149" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="K149" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>I.M.D. International Medical Devices S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.9</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -7460,12 +7460,12 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -7475,30 +7475,30 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>IT0004176001</t>
+          <t>IT0005549255</t>
         </is>
       </c>
       <c r="H150" t="n">
-        <v>104.6999969482422</v>
+        <v>1.379999995231628</v>
       </c>
       <c r="I150" t="n">
-        <v>0.8595988789234726</v>
+        <v>5.072463785643038</v>
       </c>
       <c r="J150" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="K150" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>1.7208</v>
+        <v>0.5</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -7522,14 +7522,14 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>IT0005239360</t>
+          <t>IT0004998065</t>
         </is>
       </c>
       <c r="H151" t="n">
-        <v>62.65999984741211</v>
+        <v>6.639999866485596</v>
       </c>
       <c r="I151" t="n">
-        <v>2.746249607708976</v>
+        <v>7.530120633340297</v>
       </c>
       <c r="J151" t="n">
         <v>14</v>
@@ -7541,11 +7541,11 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>I.CO.P. S.p.A. Società Benefit</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.14</v>
+        <v>0.65</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -7569,30 +7569,30 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>IT0001214433</t>
+          <t>IT0004776628</t>
         </is>
       </c>
       <c r="H152" t="n">
-        <v>23</v>
+        <v>17.72999954223633</v>
       </c>
       <c r="I152" t="n">
-        <v>0.6086956521739131</v>
+        <v>3.666102745527843</v>
       </c>
       <c r="J152" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="K152" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.06</v>
+        <v>0.54</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -7601,12 +7601,12 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -7616,30 +7616,30 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>IT0005418204</t>
+          <t>IT0005218380</t>
         </is>
       </c>
       <c r="H153" t="n">
-        <v>1.480000019073486</v>
+        <v>12.05000019073486</v>
       </c>
       <c r="I153" t="n">
-        <v>4.05405400180747</v>
+        <v>4.481327729896645</v>
       </c>
       <c r="J153" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="K153" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Confinvest F.L. S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.034</v>
+        <v>0.1</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -7648,12 +7648,12 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -7663,30 +7663,30 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>IT0005379604</t>
+          <t>NL0015435975</t>
         </is>
       </c>
       <c r="H154" t="n">
-        <v>1.889999985694885</v>
+        <v>6.245999813079834</v>
       </c>
       <c r="I154" t="n">
-        <v>1.798941812557709</v>
+        <v>1.601024703692572</v>
       </c>
       <c r="J154" t="n">
-        <v>-7</v>
+        <v>14</v>
       </c>
       <c r="K154" t="n">
-        <v>-5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.26</v>
+        <v>0.16</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -7695,81 +7695,551 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Interim</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>IT0003132476</t>
+          <t>IT0005215329</t>
         </is>
       </c>
       <c r="H155" t="n">
-        <v>24.68499946594238</v>
+        <v>8.319999694824219</v>
       </c>
       <c r="I155" t="n">
-        <v>1.053271240125887</v>
+        <v>1.923076993614967</v>
       </c>
       <c r="J155" t="n">
-        <v>-14</v>
+        <v>14</v>
       </c>
       <c r="K155" t="n">
-        <v>-12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
+          <t>Ferrari N.V.</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>3.615</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>NL0011585146</t>
+        </is>
+      </c>
+      <c r="H156" t="n">
+        <v>295.5</v>
+      </c>
+      <c r="I156" t="n">
+        <v>1.223350253807107</v>
+      </c>
+      <c r="J156" t="n">
+        <v>14</v>
+      </c>
+      <c r="K156" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Generalfinance S.p.A.</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>IT0005144784</t>
+        </is>
+      </c>
+      <c r="H157" t="n">
+        <v>27</v>
+      </c>
+      <c r="I157" t="n">
+        <v>5.037037037037037</v>
+      </c>
+      <c r="J157" t="n">
+        <v>14</v>
+      </c>
+      <c r="K157" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>MAIRE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>IT0004931058</t>
+        </is>
+      </c>
+      <c r="H158" t="n">
+        <v>13.84000015258789</v>
+      </c>
+      <c r="I158" t="n">
+        <v>4.226878566114849</v>
+      </c>
+      <c r="J158" t="n">
+        <v>14</v>
+      </c>
+      <c r="K158" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>IT0000062957</t>
+        </is>
+      </c>
+      <c r="H159" t="n">
+        <v>16.53499984741211</v>
+      </c>
+      <c r="I159" t="n">
+        <v>3.810099823488061</v>
+      </c>
+      <c r="J159" t="n">
+        <v>14</v>
+      </c>
+      <c r="K159" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Prysmian S.p.A.</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>IT0004176001</t>
+        </is>
+      </c>
+      <c r="H160" t="n">
+        <v>104.6999969482422</v>
+      </c>
+      <c r="I160" t="n">
+        <v>0.8595988789234726</v>
+      </c>
+      <c r="J160" t="n">
+        <v>14</v>
+      </c>
+      <c r="K160" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Unicredit S.p.A.</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>1.7208</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>IT0005239360</t>
+        </is>
+      </c>
+      <c r="H161" t="n">
+        <v>62.65999984741211</v>
+      </c>
+      <c r="I161" t="n">
+        <v>2.746249607708976</v>
+      </c>
+      <c r="J161" t="n">
+        <v>14</v>
+      </c>
+      <c r="K161" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>I.CO.P. S.p.A. Società Benefit</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>IT0001214433</t>
+        </is>
+      </c>
+      <c r="H162" t="n">
+        <v>23</v>
+      </c>
+      <c r="I162" t="n">
+        <v>0.6086956521739131</v>
+      </c>
+      <c r="J162" t="n">
+        <v>7</v>
+      </c>
+      <c r="K162" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Reti S.p.A.</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>IT0005418204</t>
+        </is>
+      </c>
+      <c r="H163" t="n">
+        <v>1.480000019073486</v>
+      </c>
+      <c r="I163" t="n">
+        <v>4.05405400180747</v>
+      </c>
+      <c r="J163" t="n">
+        <v>7</v>
+      </c>
+      <c r="K163" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Confinvest F.L. S.p.A.</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>IT0005379604</t>
+        </is>
+      </c>
+      <c r="H164" t="n">
+        <v>1.889999985694885</v>
+      </c>
+      <c r="I164" t="n">
+        <v>1.798941812557709</v>
+      </c>
+      <c r="J164" t="n">
+        <v>-7</v>
+      </c>
+      <c r="K164" t="n">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Eni S.p.A.</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Interim</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>IT0003132476</t>
+        </is>
+      </c>
+      <c r="H165" t="n">
+        <v>24.68499946594238</v>
+      </c>
+      <c r="I165" t="n">
+        <v>1.053271240125887</v>
+      </c>
+      <c r="J165" t="n">
+        <v>-14</v>
+      </c>
+      <c r="K165" t="n">
+        <v>-12</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
           <t>STMicroelectronics N.V.</t>
         </is>
       </c>
-      <c r="B156" t="n">
+      <c r="B166" t="n">
         <v>0.09</v>
       </c>
-      <c r="C156" t="inlineStr">
+      <c r="C166" t="inlineStr">
         <is>
           <t>DOLLARI USA</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr">
+      <c r="D166" t="inlineStr">
         <is>
           <t>2026-03-23</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr">
+      <c r="E166" t="inlineStr">
         <is>
           <t>2026-03-25</t>
         </is>
       </c>
-      <c r="F156" t="inlineStr">
+      <c r="F166" t="inlineStr">
         <is>
           <t>Interim</t>
         </is>
       </c>
-      <c r="G156" t="inlineStr">
+      <c r="G166" t="inlineStr">
         <is>
           <t>NL0000226223</t>
         </is>
       </c>
-      <c r="H156" t="n">
+      <c r="H166" t="n">
         <v>29.08499908447266</v>
       </c>
-      <c r="I156" t="n">
+      <c r="I166" t="n">
         <v>0.309437864304584</v>
       </c>
-      <c r="J156" t="n">
+      <c r="J166" t="n">
         <v>-14</v>
       </c>
-      <c r="K156" t="n">
+      <c r="K166" t="n">
         <v>-12</v>
       </c>
     </row>
@@ -7784,7 +8254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C473"/>
+  <dimension ref="A1:C493"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8028,7 +8498,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Masi Agricola S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -8038,7 +8508,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -8062,7 +8532,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>Masi Agricola S.p.A.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -8072,7 +8542,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -8130,7 +8600,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -8140,14 +8610,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BASTOGI S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -8157,14 +8627,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -8181,7 +8651,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Telesia S.p.A.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -8191,14 +8661,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Telesia S.p.A.</t>
+          <t>Triboo S.p.A.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -8215,7 +8685,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Triboo S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -8225,7 +8695,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -8283,7 +8753,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -8293,14 +8763,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -8310,14 +8780,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -8334,7 +8804,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -8344,14 +8814,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -8361,14 +8831,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>KME Group S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -8378,14 +8848,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>KME Group S.p.A.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -8395,7 +8865,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -8419,7 +8889,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Itway S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -8429,14 +8899,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Autostrade Meridionali S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -8453,7 +8923,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -8463,14 +8933,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -8480,14 +8950,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>CULTI Milano S.p.A.</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -8497,14 +8967,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -8514,14 +8984,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -8531,14 +9001,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>Autostrade Meridionali S.p.A.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -8555,7 +9025,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CULTI Milano S.p.A.</t>
+          <t>Itway S.p.A.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -8572,7 +9042,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -8582,14 +9052,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>OVS S.p.A.</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -8599,14 +9069,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>TESSELLIS S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -8616,14 +9086,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -8657,7 +9127,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -8667,14 +9137,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>OVS S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -8684,14 +9154,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -8701,7 +9171,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -8725,7 +9195,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -8759,7 +9229,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -8769,14 +9239,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>TESSELLIS S.p.A.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -8786,14 +9256,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -8810,7 +9280,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -8827,7 +9297,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -8844,7 +9314,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -8861,7 +9331,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -8871,14 +9341,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -8888,14 +9358,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -8905,14 +9375,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -8922,14 +9392,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -8946,7 +9416,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -8956,14 +9426,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -8973,7 +9443,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -9133,7 +9603,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>Ubaldi Costruzioni S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -9143,14 +9613,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Ubaldi Costruzioni S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -9167,7 +9637,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -9194,7 +9664,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -9218,7 +9688,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>CALTAGIRONE EDITORE S.p.A.</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -9235,7 +9705,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>I.M.D. International Medical Devices S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -9252,7 +9722,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>CALTAGIRONE EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -9269,7 +9739,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -9286,7 +9756,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>I.M.D. International Medical Devices S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -9303,7 +9773,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9320,7 +9790,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9330,14 +9800,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Ubaldi Costruzioni S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9347,14 +9817,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>Ubaldi Costruzioni S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9371,7 +9841,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9381,14 +9851,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9398,14 +9868,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9415,14 +9885,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9432,14 +9902,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9449,14 +9919,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9473,7 +9943,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9483,14 +9953,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9500,7 +9970,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -9524,7 +9994,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9534,14 +10004,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9558,7 +10028,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9575,7 +10045,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9592,7 +10062,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9609,7 +10079,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9626,7 +10096,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9643,7 +10113,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9660,7 +10130,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9677,7 +10147,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9694,7 +10164,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>Egomnia S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9711,7 +10181,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9721,14 +10191,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9745,7 +10215,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9762,7 +10232,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>gAIn360 S.p.A.</t>
+          <t>I.M.D. International Medical Devices S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9779,7 +10249,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9789,14 +10259,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9813,7 +10283,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9830,7 +10300,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9847,7 +10317,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9881,7 +10351,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9898,7 +10368,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9932,7 +10402,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -9949,7 +10419,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -9966,7 +10436,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -9983,7 +10453,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10000,7 +10470,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>I.M.D. International Medical Devices S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10017,7 +10487,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10034,7 +10504,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>gAIn360 S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10051,7 +10521,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10068,7 +10538,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10078,14 +10548,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10102,7 +10572,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10119,7 +10589,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10129,14 +10599,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10153,7 +10623,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10170,7 +10640,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Egomnia S.p.A.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -10187,7 +10657,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -10197,14 +10667,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -10221,7 +10691,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -10238,7 +10708,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -10248,14 +10718,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>NEXT RE SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -10272,7 +10742,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>AEDES S.p.A.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -10289,7 +10759,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
+          <t>Monnalisa S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -10306,7 +10776,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -10316,14 +10786,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -10333,14 +10803,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Franchi Umberto Marmi S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -10350,14 +10820,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -10367,14 +10837,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -10391,7 +10861,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>AEDES S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -10408,7 +10878,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>NEXT RE SIIQ S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -10418,14 +10888,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -10442,7 +10912,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -10459,7 +10929,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10476,7 +10946,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10493,7 +10963,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Monnalisa S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10503,14 +10973,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10527,7 +10997,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10544,7 +11014,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Gambero Rosso S.p.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10561,7 +11031,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Grifal S.p.A.</t>
+          <t>rino petino S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10578,7 +11048,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10595,7 +11065,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10605,14 +11075,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10629,7 +11099,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Longino &amp; Cardenal S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10646,7 +11116,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10663,7 +11133,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>RES S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10673,14 +11143,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>FRENDY ENERGY S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10697,7 +11167,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -10714,7 +11184,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -10731,7 +11201,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -10741,14 +11211,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>Braga Moro Sistemi di Energia S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -10765,7 +11235,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -10782,7 +11252,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -10799,7 +11269,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -10816,7 +11286,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -10833,7 +11303,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -10843,14 +11313,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>rino petino S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -10867,7 +11337,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -10884,7 +11354,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>RES S.p.A.</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -10901,12 +11371,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>Allcore S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -10918,12 +11388,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -10935,12 +11405,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -10952,12 +11422,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>Longino &amp; Cardenal S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -10969,12 +11439,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -10986,12 +11456,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>ISCC FINTECH S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -11003,12 +11473,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Gambero Rosso S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -11020,12 +11490,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>Grifal S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -11037,12 +11507,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>FRENDY ENERGY S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -11054,12 +11524,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>Gambero Rosso S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -11071,7 +11541,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>VINEXT S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -11088,7 +11558,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -11105,7 +11575,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>Telmes S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -11122,7 +11592,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -11139,7 +11609,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -11173,7 +11643,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -11190,7 +11660,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -11207,7 +11677,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -11224,7 +11694,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -11234,14 +11704,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -11258,7 +11728,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>Gambero Rosso S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -11275,7 +11745,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -11285,14 +11755,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -11309,7 +11779,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -11326,7 +11796,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -11343,7 +11813,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -11360,7 +11830,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -11370,14 +11840,14 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -11394,7 +11864,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>VINEXT S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -11411,7 +11881,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -11428,7 +11898,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Telmes S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -11445,7 +11915,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -11462,7 +11932,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>BolognaFiere S.p.A.</t>
+          <t>OLIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -11472,14 +11942,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -11496,7 +11966,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -11513,7 +11983,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -11530,7 +12000,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -11547,7 +12017,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -11557,14 +12027,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -11581,7 +12051,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -11591,14 +12061,14 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -11615,7 +12085,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -11632,7 +12102,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -11642,14 +12112,14 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -11666,7 +12136,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>TECMA SOLUTIONS S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -11683,7 +12153,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -11700,7 +12170,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>OLIDATA S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -11710,14 +12180,14 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -11727,14 +12197,14 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -11744,14 +12214,14 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -11768,7 +12238,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Cogefeed S.p.A.</t>
+          <t>ISCC FINTECH S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -11785,7 +12255,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -11802,7 +12272,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -11836,7 +12306,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -11853,7 +12323,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -11870,12 +12340,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>Cogefeed S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -11887,12 +12357,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>MIT SIM S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -11904,12 +12374,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>TECMA SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -11921,12 +12391,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -11938,12 +12408,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -11955,12 +12425,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -11972,12 +12442,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Pasquarelli Auto S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -11989,29 +12459,29 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>MONDO TV S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -12023,24 +12493,24 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -12057,7 +12527,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -12067,14 +12537,14 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -12091,7 +12561,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -12108,7 +12578,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>Bellini Nautica S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -12125,7 +12595,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -12142,7 +12612,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>BolognaFiere S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -12159,7 +12629,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Bellini Nautica S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -12176,7 +12646,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -12193,7 +12663,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -12210,7 +12680,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>ELSA Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -12227,7 +12697,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>Pasquarelli Auto S.p.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -12244,7 +12714,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -12254,14 +12724,14 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -12278,7 +12748,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -12295,7 +12765,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -12312,7 +12782,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -12329,7 +12799,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>E.P.H. S.p.A.</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -12339,14 +12809,14 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -12363,7 +12833,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -12373,14 +12843,14 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Haiki+ S.p.A.</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -12397,7 +12867,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -12414,7 +12884,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>Confinvest F.L. S.p.A.</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -12431,7 +12901,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -12441,14 +12911,14 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -12465,7 +12935,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -12482,7 +12952,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -12499,7 +12969,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -12516,7 +12986,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -12526,14 +12996,14 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -12550,7 +13020,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -12567,7 +13037,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>YOLO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -12584,7 +13054,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -12601,7 +13071,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -12618,7 +13088,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>MIT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -12635,7 +13105,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -12652,7 +13122,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>MONDO TV S.p.A.</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -12662,14 +13132,14 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -12686,7 +13156,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -12703,7 +13173,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>YOLO GROUP S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -12720,7 +13190,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -12730,14 +13200,14 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -12754,7 +13224,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -12771,7 +13241,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -12781,14 +13251,14 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -12798,14 +13268,14 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -12822,7 +13292,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -12839,7 +13309,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -12856,7 +13326,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -12866,14 +13336,14 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -12890,7 +13360,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -12907,7 +13377,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -12924,7 +13394,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -12934,14 +13404,14 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -12958,7 +13428,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Confinvest F.L. S.p.A.</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -12975,7 +13445,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -12992,7 +13462,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -13009,7 +13479,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -13026,7 +13496,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>GPI S.p.A.</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -13043,7 +13513,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -13060,7 +13530,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -13077,7 +13547,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -13094,7 +13564,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>INNOVATEC S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -13104,14 +13574,14 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>Haiki+ S.p.A.</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -13128,7 +13598,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -13145,7 +13615,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>INNOVATEC S.p.A.</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -13162,7 +13632,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -13179,7 +13649,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -13196,7 +13666,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -13213,7 +13683,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Lindbergh S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -13230,7 +13700,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -13247,7 +13717,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -13264,7 +13734,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>E.P.H. S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -13274,14 +13744,14 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -13298,7 +13768,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -13315,7 +13785,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -13325,14 +13795,14 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>ELSA Solutions S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -13349,7 +13819,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -13366,7 +13836,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>EUKEDOS S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -13376,14 +13846,14 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -13393,14 +13863,14 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Lindbergh S.p.A.</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -13410,19 +13880,19 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>Leone Film Group S.p.A.</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -13434,12 +13904,12 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -13451,12 +13921,12 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -13468,29 +13938,29 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -13502,12 +13972,12 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -13519,12 +13989,12 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -13536,12 +14006,12 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -13553,12 +14023,12 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -13570,12 +14040,12 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -13587,7 +14057,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -13604,7 +14074,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -13621,7 +14091,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -13631,14 +14101,14 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -13655,7 +14125,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -13672,7 +14142,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -13689,7 +14159,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>Next Geosolutions Europe S.p.A.</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -13706,7 +14176,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Cogefeed S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -13723,7 +14193,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Com.Tel S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -13740,7 +14210,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -13757,7 +14227,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -13774,7 +14244,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -13791,7 +14261,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -13808,7 +14278,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -13825,7 +14295,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>TMP Group S.p.A.</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -13835,14 +14305,14 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -13859,7 +14329,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -13869,14 +14339,14 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>WEBSOLUTE S.p.A.</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -13886,14 +14356,14 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Somec S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -13910,7 +14380,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -13927,7 +14397,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>Emma Villas S.p.A.</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -13944,7 +14414,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -13961,7 +14431,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -13978,7 +14448,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>Finanza.tech S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -13995,7 +14465,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -14005,14 +14475,14 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -14022,14 +14492,14 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -14046,7 +14516,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -14063,7 +14533,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -14080,7 +14550,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -14097,7 +14567,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>STAR7 S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -14114,7 +14584,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>AATECH S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -14131,7 +14601,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -14148,7 +14618,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Softlab S.p.A.</t>
+          <t>FRANCHETTI S.p.A.</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -14158,14 +14628,14 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -14175,14 +14645,14 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -14199,7 +14669,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -14216,7 +14686,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -14233,7 +14703,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Eprcomunicazione S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -14250,7 +14720,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -14267,7 +14737,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>Reway Group S.p.A.</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -14284,7 +14754,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -14301,7 +14771,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -14318,7 +14788,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>GEL S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -14335,7 +14805,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -14352,7 +14822,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>ESI S.p.A.</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -14369,7 +14839,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -14386,7 +14856,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -14396,14 +14866,14 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -14420,7 +14890,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>ESI S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -14437,7 +14907,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -14454,7 +14924,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -14471,7 +14941,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -14488,7 +14958,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -14505,7 +14975,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -14522,7 +14992,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -14539,7 +15009,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>WEBSOLUTE S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -14556,7 +15026,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -14573,7 +15043,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -14590,7 +15060,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>Cogefeed S.p.A.</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -14607,7 +15077,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>Com.Tel S.p.A.</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -14624,12 +15094,12 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -14641,12 +15111,12 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -14658,12 +15128,12 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -14675,12 +15145,12 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>STAR7 S.p.A.</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -14692,46 +15162,46 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>Società Editoriale il Fatto S.p.A.</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -14743,29 +15213,29 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>GEL S.p.A.</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -14777,12 +15247,12 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -14794,29 +15264,29 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -14828,12 +15298,12 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -14845,12 +15315,12 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -14862,46 +15332,46 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>Somec S.p.A.</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -14913,12 +15383,12 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -14930,97 +15400,97 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>Softlab S.p.A.</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -15032,63 +15502,63 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -15100,12 +15570,12 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -15117,12 +15587,12 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -15134,46 +15604,46 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -15185,29 +15655,29 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>CALTAGIRONE EDITORE S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -15219,12 +15689,12 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -15236,29 +15706,29 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -15270,12 +15740,12 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -15287,7 +15757,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -15297,14 +15767,14 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>TECMA SOLUTIONS S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -15314,14 +15784,14 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -15338,7 +15808,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -15348,14 +15818,14 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -15365,14 +15835,14 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -15382,14 +15852,14 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>CALTAGIRONE EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -15406,63 +15876,63 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -15474,29 +15944,29 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -15508,63 +15978,63 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -15576,177 +16046,177 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>TRAWELL CO S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>TECMA SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
@@ -15756,14 +16226,14 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -15773,14 +16243,14 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -15807,24 +16277,364 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
+          <t>Davide Campari-Milano N.V.</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>CELLULARLINE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>CELLULARLINE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>Banca Generali S.p.A.</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>ZIGNAGO VETRO S.p.A.</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>EL.EN. S.p.A.</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>Bper Banca S.P.A.</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
           <t>Ariston Holding N.V.</t>
         </is>
       </c>
-      <c r="B473" t="inlineStr">
+      <c r="B480" t="inlineStr">
         <is>
           <t>2026-05-06</t>
         </is>
       </c>
-      <c r="C473" t="inlineStr">
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>Arterra Bioscience S.p.A.</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>Industrie De Nora S.p.A.</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
         <is>
           <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>Industrie De Nora S.p.A.</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>Lottomatica Group S.p.A.</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>Nexi S.p.A.</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>Poste Italiane S.p.A.</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>TECHNOGYM S.p.A.</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>TECHNOGYM S.p.A.</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>TELECOM ITALIA S.p.A.</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>TRAWELL CO S.p.A.</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>Ariston Holding N.V.</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>Esprinet S.p.A.</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>FinecoBank S.p.A.</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -15852,452 +16662,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Ariston Holding N.V.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Ariston Holding N.V.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Arterra Bioscience S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Banca Generali S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Bper Banca S.P.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>CELLULARLINE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>CELLULARLINE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Davide Campari-Milano N.V.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Davide Campari-Milano N.V.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>EDISON S.p.A.</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>EL.EN. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Eni S.p.A.</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Esprinet S.p.A.</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>FinecoBank S.p.A.</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Industrie De Nora S.p.A.</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Industrie De Nora S.p.A.</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Lottomatica Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Nexi S.p.A.</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Poste Italiane S.p.A.</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>TECHNOGYM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>TECHNOGYM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>TELECOM ITALIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>TRAWELL CO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>